--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484373_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484373_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6489</v>
+        <v>3.1065</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6807</v>
+        <v>4.4379</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0318</v>
+        <v>-1.3314</v>
       </c>
       <c r="G2" t="n">
         <v>4.1181</v>
@@ -610,13 +610,13 @@
         <v>0.7814</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0319</v>
+        <v>-0.5743</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0083</v>
+        <v>-0.2345</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0403</v>
+        <v>-0.3399</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2186</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BATALLER ABULI</t>
+          <t>A. RIVAS POMEROL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.753</v>
+        <v>0.632</v>
       </c>
       <c r="E4" t="n">
-        <v>1.226</v>
+        <v>2.368</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4731</v>
+        <v>-1.736</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3826</v>
+        <v>1.8149</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6429</v>
+        <v>1.6805</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0255</v>
+        <v>0.1344</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5397</v>
+        <v>3.1232</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2714</v>
+        <v>2.988</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2683</v>
+        <v>0.1352</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9223</v>
+        <v>-1.3083</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-1.3075</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2937</v>
+        <v>-0.0008</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7138</v>
+        <v>-1.0462</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0305</v>
+        <v>-0.665</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6833</v>
+        <v>-0.3812</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0078</v>
+        <v>-0.3321</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6093</v>
+        <v>0.8865</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3985</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RIVAS POMEROL</t>
+          <t>J. BATALLER ABULI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4103</v>
+        <v>0.1445</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0647</v>
+        <v>0.781</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6543</v>
+        <v>-0.6365</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8149</v>
+        <v>-0.3826</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6805</v>
+        <v>0.6429</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1344</v>
+        <v>-1.0255</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1232</v>
+        <v>2.5397</v>
       </c>
       <c r="K5" t="n">
-        <v>2.988</v>
+        <v>1.2714</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1352</v>
+        <v>1.2683</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3083</v>
+        <v>-2.9223</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3075</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0008</v>
+        <v>-2.2937</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2678</v>
+        <v>0.1053</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9684</v>
+        <v>-0.4146</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2995</v>
+        <v>0.5199</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3321</v>
+        <v>1.0078</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8865</v>
+        <v>0.6093</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>0.3985</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8117</v>
+        <v>-0.6016</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3715</v>
+        <v>-0.2704</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4402</v>
+        <v>-0.3312</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4488</v>
@@ -922,13 +922,13 @@
         <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4763</v>
+        <v>-1.2663</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.773</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7033</v>
+        <v>-0.5944</v>
       </c>
       <c r="V6" t="n">
         <v>0.9414</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4981</v>
+        <v>-2.0314</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7032</v>
+        <v>2.0065</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.2013</v>
+        <v>-4.0379</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0038</v>
@@ -1000,13 +1000,13 @@
         <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4125</v>
+        <v>-0.9457</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2105</v>
+        <v>-0.9071</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.202</v>
+        <v>-0.0386</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2772</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6156</v>
+        <v>-2.2712</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.4</v>
+        <v>-3.1373</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7844</v>
+        <v>0.8661</v>
       </c>
       <c r="G8" t="n">
         <v>-1.963</v>
@@ -1078,13 +1078,13 @@
         <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4573</v>
+        <v>-0.1128</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6052</v>
+        <v>-0.3425</v>
       </c>
       <c r="U8" t="n">
-        <v>0.148</v>
+        <v>0.2297</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9661</v>
+        <v>-2.546</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3911</v>
+        <v>-0.1889</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.575</v>
+        <v>-2.3571</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9551</v>
@@ -1156,13 +1156,13 @@
         <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1946</v>
+        <v>-0.7745</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0289</v>
+        <v>-0.8267</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1657</v>
+        <v>0.0522</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5977</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1905</v>
+        <v>-2.9805</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4455</v>
+        <v>-2.3444</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.745</v>
+        <v>-0.636</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2318</v>
@@ -1234,13 +1234,13 @@
         <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2438</v>
+        <v>-0.0337</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1816</v>
+        <v>-0.0805</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0622</v>
+        <v>0.0467</v>
       </c>
       <c r="V10" t="n">
         <v>0.0664</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3537</v>
+        <v>-4.688</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2958</v>
+        <v>-2.9025</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0578</v>
+        <v>-1.7855</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6395</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1127</v>
+        <v>-0.447</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4541</v>
+        <v>-0.1526</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5668</v>
+        <v>-0.2945</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8201000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0468</v>
+        <v>-5.5698</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3732</v>
+        <v>-4.5149</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6736</v>
+        <v>-1.0549</v>
       </c>
       <c r="G12" t="n">
         <v>-4.8392</v>
@@ -1390,13 +1390,13 @@
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4721</v>
+        <v>-0.0509</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.341</v>
+        <v>-0.4827</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8131</v>
+        <v>0.4318</v>
       </c>
       <c r="V12" t="n">
         <v>-0.875</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2848</v>
+        <v>-5.8471</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5894</v>
+        <v>-4.1244</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6954</v>
+        <v>-1.7227</v>
       </c>
       <c r="G13" t="n">
         <v>-4.8292</v>
@@ -1468,13 +1468,13 @@
         <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6509</v>
+        <v>-0.2132</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8941</v>
+        <v>-0.4291</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2431</v>
+        <v>0.2159</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6093</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.9705</v>
+        <v>-21.668</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.998</v>
+        <v>-6.6955</v>
       </c>
       <c r="F14" t="n">
         <v>-14.9724</v>
@@ -1546,13 +1546,13 @@
         <v>10.7441</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.7224</v>
+        <v>-5.4198</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.5703</v>
+        <v>-5.2677</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1522999999999999</v>
+        <v>-0.1524</v>
       </c>
       <c r="V14" t="n">
         <v>-2.7144</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.8658</v>
+        <v>8.608599999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2806</v>
+        <v>6.8873</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5852</v>
+        <v>1.7213</v>
       </c>
       <c r="G15" t="n">
         <v>5.1422</v>
@@ -1624,13 +1624,13 @@
         <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2532</v>
+        <v>0.4897</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7125</v>
+        <v>-0.1058</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4593</v>
+        <v>0.5955</v>
       </c>
       <c r="V15" t="n">
         <v>1.2186</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.6984</v>
+        <v>7.2187</v>
       </c>
       <c r="E16" t="n">
-        <v>7.0824</v>
+        <v>6.5768</v>
       </c>
       <c r="F16" t="n">
-        <v>0.616</v>
+        <v>0.6418</v>
       </c>
       <c r="G16" t="n">
         <v>4.0658</v>
@@ -1702,13 +1702,13 @@
         <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>1.746</v>
+        <v>1.2663</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.4465</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.8198</v>
       </c>
       <c r="V16" t="n">
         <v>1.4959</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5522</v>
+        <v>5.1593</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0584</v>
+        <v>3.8562</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4938</v>
+        <v>1.3031</v>
       </c>
       <c r="G17" t="n">
         <v>3.4743</v>
@@ -1780,13 +1780,13 @@
         <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6872</v>
+        <v>0.2944</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.1196</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6046</v>
+        <v>0.414</v>
       </c>
       <c r="V17" t="n">
         <v>0.6093</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.6349</v>
+        <v>4.7152</v>
       </c>
       <c r="E18" t="n">
         <v>3.5874</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0474</v>
+        <v>1.1278</v>
       </c>
       <c r="G18" t="n">
         <v>2.4291</v>
@@ -1858,13 +1858,13 @@
         <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.8722</v>
       </c>
       <c r="T18" t="n">
         <v>0.1569</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6349</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>1.2186</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.4289</v>
+        <v>3.2719</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3306</v>
+        <v>2.2295</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0982</v>
+        <v>1.0424</v>
       </c>
       <c r="G19" t="n">
         <v>1.8921</v>
@@ -1936,13 +1936,13 @@
         <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6735</v>
+        <v>0.5165</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0384</v>
+        <v>-0.1395</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7119</v>
+        <v>0.656</v>
       </c>
       <c r="V19" t="n">
         <v>0.2772</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.0682</v>
+        <v>3.125</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1784</v>
+        <v>1.5829</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8898</v>
+        <v>1.5421</v>
       </c>
       <c r="G20" t="n">
         <v>2.4847</v>
@@ -2014,13 +2014,13 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7252</v>
+        <v>0.3315</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5915</v>
+        <v>-0.187</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1338</v>
+        <v>0.5185</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2772</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5672</v>
+        <v>0.339</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.608</v>
+        <v>-0.0014</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0408</v>
+        <v>0.3404</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3761</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4331</v>
+        <v>0.4732</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6657</v>
+        <v>-0.0591</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2327</v>
+        <v>0.5323</v>
       </c>
       <c r="V21" t="n">
         <v>1.2186</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.578</v>
+        <v>-2.5184</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0693</v>
+        <v>-2.6661</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4913</v>
+        <v>0.1477</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4166</v>
+        <v>-3.0313</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1059</v>
+        <v>-1.3592</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3107</v>
+        <v>-1.6721</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2664</v>
+        <v>-2.4722</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6306</v>
+        <v>-0.5308</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3642</v>
+        <v>-1.9414</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1502</v>
+        <v>-0.5591</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5247000000000001</v>
+        <v>-0.8283</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.2692</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5395</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9069</v>
+        <v>-0.1953</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6553</v>
+        <v>0.4581</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1732</v>
+        <v>0.0015</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8285</v>
+        <v>0.4566</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5545</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6688</v>
+        <v>-2.897</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4639</v>
+        <v>-4.1704</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.205</v>
+        <v>1.2734</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0313</v>
+        <v>-0.4166</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3592</v>
+        <v>-0.1059</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6721</v>
+        <v>-0.3107</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.4722</v>
+        <v>-0.2664</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5308</v>
+        <v>-0.6306</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9414</v>
+        <v>0.3642</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5591</v>
+        <v>-0.1502</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8283</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2692</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1953</v>
+        <v>-3.9069</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3076</v>
+        <v>0.3363</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2037</v>
+        <v>-0.2743</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1039</v>
+        <v>0.6107</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0549</v>
+        <v>-0.2772</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0549</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4637</v>
+        <v>-4.3778</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1271</v>
+        <v>-2.6327</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3366</v>
+        <v>-1.7452</v>
       </c>
       <c r="G24" t="n">
         <v>-1.154</v>
@@ -2326,13 +2326,13 @@
         <v>0.3907</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2725</v>
+        <v>1.3584</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9383</v>
+        <v>0.4327</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3342</v>
+        <v>0.9257</v>
       </c>
       <c r="V24" t="n">
         <v>-2.8242</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>21.9707</v>
+        <v>22.6445</v>
       </c>
       <c r="E25" t="n">
         <v>15.2495</v>
       </c>
       <c r="F25" t="n">
-        <v>6.720899999999999</v>
+        <v>7.3948</v>
       </c>
       <c r="G25" t="n">
         <v>14.5102</v>
@@ -2389,10 +2389,10 @@
         <v>-4.5705</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5189999999999999</v>
+        <v>-0.519</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.051499999999999</v>
+        <v>-4.0515</v>
       </c>
       <c r="P25" t="n">
         <v>-0.9767999999999997</v>
@@ -2404,19 +2404,19 @@
         <v>9.767100000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>5.7224</v>
+        <v>6.396599999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1523000000000001</v>
+        <v>0.1523</v>
       </c>
       <c r="U25" t="n">
-        <v>5.5701</v>
+        <v>6.2443</v>
       </c>
       <c r="V25" t="n">
         <v>2.7145</v>
       </c>
       <c r="W25" t="n">
-        <v>6.760300000000001</v>
+        <v>6.7603</v>
       </c>
       <c r="X25" t="n">
         <v>-4.0457</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484373_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484373_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>À. ANTEQUERA SOLER</t>
+          <t>A. ANTEQUERA SOLER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.3985</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.1522</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0.0664</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.8201000000000001</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.2108</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.482899999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,11 +1707,16 @@
       <c r="X15" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,28 +1728,28 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.2187</v>
+        <v>6.9117</v>
       </c>
       <c r="E16" t="n">
-        <v>6.5768</v>
+        <v>6.2698</v>
       </c>
       <c r="F16" t="n">
         <v>0.6418</v>
       </c>
       <c r="G16" t="n">
-        <v>4.0658</v>
+        <v>3.7589</v>
       </c>
       <c r="H16" t="n">
-        <v>4.0799</v>
+        <v>3.7729</v>
       </c>
       <c r="I16" t="n">
         <v>-0.014</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8298</v>
+        <v>4.5228</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7084</v>
+        <v>4.4014</v>
       </c>
       <c r="L16" t="n">
         <v>0.1214</v>
@@ -1718,6 +1789,11 @@
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,11 +2205,16 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5184</v>
+        <v>0.307</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6661</v>
+        <v>0.307</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1477</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0313</v>
+        <v>0.307</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3592</v>
+        <v>0.307</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6721</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4722</v>
+        <v>0.307</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5308</v>
+        <v>0.307</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9414</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5591</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8283</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2692</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4581</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0015</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4566</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.897</v>
+        <v>-2.5184</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1704</v>
+        <v>-2.6661</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2734</v>
+        <v>0.1477</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4166</v>
+        <v>-3.0313</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1059</v>
+        <v>-1.3592</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3107</v>
+        <v>-1.6721</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2664</v>
+        <v>-2.4722</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6306</v>
+        <v>-0.5308</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3642</v>
+        <v>-1.9414</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1502</v>
+        <v>-0.5591</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5247000000000001</v>
+        <v>-0.8283</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.2692</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.5395</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9069</v>
+        <v>-0.1953</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3363</v>
+        <v>0.4581</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2743</v>
+        <v>0.0015</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6107</v>
+        <v>0.4566</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5545</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3778</v>
+        <v>-2.897</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6327</v>
+        <v>-4.1704</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7452</v>
+        <v>1.2734</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.154</v>
+        <v>-0.4166</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.331</v>
+        <v>-0.1059</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8229</v>
+        <v>-0.3107</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.2664</v>
       </c>
       <c r="K24" t="n">
-        <v>0.023</v>
+        <v>-0.6306</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5527</v>
+        <v>0.3642</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6243</v>
+        <v>-0.1502</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.354</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2702</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.7581</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1488</v>
+        <v>-3.9069</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3584</v>
+        <v>0.3363</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4327</v>
+        <v>-0.2743</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9257</v>
+        <v>0.6107</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.8242</v>
+        <v>-0.2772</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3869</v>
+        <v>0.2772</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4373</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,152 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-4.3778</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.6327</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.7452</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.154</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.331</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.8229</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.5296999999999999</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.5527</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.6243</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.354</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.2702</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.3584</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.9257</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-2.8242</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.3869</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484373_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>22.6445</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>15.2495</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>7.3948</v>
       </c>
-      <c r="G25" t="n">
-        <v>14.5102</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="G26" t="n">
+        <v>14.5103</v>
+      </c>
+      <c r="H26" t="n">
         <v>6.416099999999999</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>8.094199999999997</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>19.0809</v>
       </c>
-      <c r="K25" t="n">
-        <v>6.935199999999999</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K26" t="n">
+        <v>6.935199999999998</v>
+      </c>
+      <c r="L26" t="n">
         <v>12.1455</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>-4.5705</v>
       </c>
-      <c r="N25" t="n">
-        <v>-0.519</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-4.0515</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="N26" t="n">
+        <v>-0.5189999999999999</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-4.051499999999999</v>
+      </c>
+      <c r="P26" t="n">
         <v>-0.9767999999999997</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>-10.7437</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>9.767100000000001</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>6.396599999999999</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>0.1523</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>6.2443</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>2.7145</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>6.7603</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>-4.0457</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
